--- a/Sample_run/1/student/hieunqhe171297/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/hieunqhe171297/TC6/GradeDetail.xlsx
@@ -164,7 +164,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -173,12 +176,6 @@
     <x:t>Server responding (SYN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
-  </x:si>
-  <x:si>
     <x:t>ACK</x:t>
   </x:si>
   <x:si>
@@ -207,18 +204,6 @@
   </x:si>
   <x:si>
     <x:t>{"StudentId":"S111","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(Not validated by this test case)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RST, ACK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Connection reset</x:t>
-  </x:si>
-  <x:si>
-    <x:t>INFO</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -245,7 +230,7 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -254,17 +239,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFB6C1"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -287,7 +262,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -297,14 +272,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -314,14 +283,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -981,11 +942,11 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:R25"/>
+  <x:dimension ref="A1:R23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="5.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="28.996339" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="5.139196" style="0" customWidth="1"/>
     <x:col min="3" max="3" width="4.424911" style="0" customWidth="1"/>
     <x:col min="4" max="4" width="6.853482" style="0" customWidth="1"/>
     <x:col min="5" max="5" width="11.139196" style="0" customWidth="1"/>
@@ -995,7 +956,7 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
     <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
@@ -1092,28 +1053,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>48036</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1133,10 +1094,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1148,7 +1109,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
         <x:v>17</x:v>
@@ -1168,8 +1129,8 @@
       <x:c r="Q3" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R3" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R3" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1189,10 +1150,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1204,7 +1165,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
         <x:v>17</x:v>
@@ -1224,8 +1185,8 @@
       <x:c r="Q4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R4" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R4" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1245,13 +1206,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s">
+      <x:c r="H5" s="0" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>46</x:v>
@@ -1260,7 +1221,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
         <x:v>17</x:v>
@@ -1280,8 +1241,8 @@
       <x:c r="Q5" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R5" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R5" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1301,10 +1262,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1316,7 +1277,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
         <x:v>17</x:v>
@@ -1336,8 +1297,8 @@
       <x:c r="Q6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R6" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R6" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1357,13 +1318,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>47</x:v>
@@ -1372,7 +1333,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
         <x:v>17</x:v>
@@ -1392,8 +1353,8 @@
       <x:c r="Q7" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R7" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1413,10 +1374,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1428,7 +1389,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
         <x:v>17</x:v>
@@ -1448,8 +1409,8 @@
       <x:c r="Q8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R8" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R8" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1469,10 +1430,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1484,7 +1445,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
         <x:v>17</x:v>
@@ -1504,8 +1465,8 @@
       <x:c r="Q9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R9" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1525,10 +1486,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1540,7 +1501,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
         <x:v>17</x:v>
@@ -1560,8 +1521,8 @@
       <x:c r="Q10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R10" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R10" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1581,10 +1542,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1596,7 +1557,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
         <x:v>17</x:v>
@@ -1616,8 +1577,8 @@
       <x:c r="Q11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R11" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1637,10 +1598,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1652,7 +1613,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
         <x:v>17</x:v>
@@ -1672,8 +1633,8 @@
       <x:c r="Q12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R12" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1708,28 +1669,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P13" s="0">
-        <x:v>39190</x:v>
-      </x:c>
-      <x:c r="Q13" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q13" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:18">
@@ -1749,10 +1710,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
         <x:v>17</x:v>
@@ -1764,7 +1725,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
         <x:v>17</x:v>
@@ -1784,8 +1745,8 @@
       <x:c r="Q14" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R14" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R14" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:18">
@@ -1805,10 +1766,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G15" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>17</x:v>
@@ -1820,7 +1781,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
         <x:v>17</x:v>
@@ -1840,8 +1801,8 @@
       <x:c r="Q15" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R15" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R15" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:18">
@@ -1861,13 +1822,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G16" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>46</x:v>
@@ -1876,7 +1837,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
         <x:v>17</x:v>
@@ -1896,8 +1857,8 @@
       <x:c r="Q16" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R16" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R16" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:18">
@@ -1917,10 +1878,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G17" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>17</x:v>
@@ -1932,7 +1893,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
         <x:v>17</x:v>
@@ -1952,8 +1913,8 @@
       <x:c r="Q17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R17" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R17" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:18">
@@ -1973,13 +1934,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="G18" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>47</x:v>
@@ -1988,7 +1949,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
         <x:v>17</x:v>
@@ -2008,8 +1969,8 @@
       <x:c r="Q18" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R18" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R18" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -2029,10 +1990,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G19" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>17</x:v>
@@ -2044,7 +2005,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
         <x:v>17</x:v>
@@ -2064,8 +2025,8 @@
       <x:c r="Q19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R19" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R19" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:18">
@@ -2085,10 +2046,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>17</x:v>
@@ -2100,7 +2061,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
         <x:v>17</x:v>
@@ -2120,8 +2081,8 @@
       <x:c r="Q20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R20" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2141,10 +2102,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G21" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>17</x:v>
@@ -2156,7 +2117,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
         <x:v>17</x:v>
@@ -2176,8 +2137,8 @@
       <x:c r="Q21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R21" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R21" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:18">
@@ -2197,10 +2158,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
@@ -2212,7 +2173,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
         <x:v>17</x:v>
@@ -2232,8 +2193,8 @@
       <x:c r="Q22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R22" s="3" t="s">
-        <x:v>52</x:v>
+      <x:c r="R22" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2253,10 +2214,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="G23" s="0" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>17</x:v>
@@ -2268,7 +2229,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
         <x:v>17</x:v>
@@ -2288,120 +2249,8 @@
       <x:c r="Q23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R23" s="3" t="s">
-        <x:v>52</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:18">
-      <x:c r="A24" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B24" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K24" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="L24" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="M24" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N24" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O24" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P24" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q24" s="0">
-        <x:v>48036</x:v>
-      </x:c>
-      <x:c r="R24" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:18">
-      <x:c r="A25" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B25" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="I25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="J25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="K25" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="L25" s="0" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="M25" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N25" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O25" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P25" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q25" s="0">
-        <x:v>39190</x:v>
-      </x:c>
-      <x:c r="R25" s="4" t="s">
-        <x:v>66</x:v>
+      <x:c r="R23" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
